--- a/data/reference_rates_2026-08-07.xlsx
+++ b/data/reference_rates_2026-08-07.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>46242.81875077546</v>
+        <v>46242.83060642361</v>
       </c>
     </row>
     <row r="5">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>46242.81875346065</v>
+        <v>46242.83060650463</v>
       </c>
     </row>
     <row r="6">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>46242.81875609954</v>
+        <v>46242.83060659722</v>
       </c>
     </row>
     <row r="7">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46242.81875914352</v>
+        <v>46242.83060667824</v>
       </c>
     </row>
   </sheetData>
@@ -787,7 +787,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-08 19:39:00</t>
+          <t>2026-08-08 19:56:04</t>
         </is>
       </c>
     </row>
